--- a/docs/test/unit/NOUS-102/観点表_promptBuilder_tokenEstimator.xlsx
+++ b/docs/test/unit/NOUS-102/観点表_promptBuilder_tokenEstimator.xlsx
@@ -4234,7 +4234,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>正常系</t>
+          <t>異常系</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -4244,18 +4244,18 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>参照する投稿をすべて外しても、候補の reply・like はそのまま入力に残る</t>
+          <t>上限のために参照する投稿をすべて外したときは、reply・like を候補から外す</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
           <t>前提：リポジトリの prompts/v1
-入力：長い本文の投稿 1 件、候補 reply・like、上限 = 投稿なしの見積もり</t>
+入力：長い本文の投稿 1 件、候補 reply・like・post、上限 = 投稿なしの見積もり</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>refs は []、system に「reply・like」、user に「（まだ投稿はありません）」</t>
+          <t>refs は []、user に「（まだ投稿はありません）」。system の候補は post だけ（「今回選べる行動は post です」）で、reply・like の選び方の目安を含まない</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -4272,7 +4272,7 @@
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_PRM-031 参照する投稿をすべて外しても、候補の reply・like はそのまま入力に残る</t>
+          <t>TC-UT_PRM-031 上限のために参照する投稿をすべて外したときは、reply・like を候補から外す</t>
         </is>
       </c>
       <c r="N56" s="6" t="inlineStr">
@@ -4285,7 +4285,8 @@
       <c r="Q56" s="7" t="inlineStr">
         <is>
           <t>既存テスト：なし
-設計書は候補の抽選（drawCandidates）を buildPrompt の前に行う順序だけを定め、投稿を外しきったときの候補の扱いは記載なし。実装の値。issues の確認事項 1</t>
+疑い：今の buildPrompt は受け取った候補をそのまま入れるため、投稿を外しきっても system に reply・like が残る（実施のときに NG になる見込み）
+仕様は 2026-10-23 NOUS-102 で Kouhei Tajima が決定（候補に入れる条件「参照できる投稿があること」を、外した後の状態で判断する）。issues の疑い 1</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5750,7 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>参照する投稿をすべて外しても、候補の reply・like はそのまま入力に残る</t>
+          <t>上限のために参照する投稿をすべて外したときは、reply・like を候補から外す</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
@@ -5853,7 +5854,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>apps/server/src/generation/promptBuilder.test.ts・tokenEstimator.test.ts（実装時、NOUS-61）, apps/server/src/generation/promptBuilder.ut.test.ts・tokenEstimator.ut.test.ts（単体テストで追加）</t>
+          <t>apps/server/src/generation/promptBuilder.test.ts（実装時、NOUS-61）, apps/server/src/generation/tokenEstimator.test.ts（実装時、NOUS-61）, apps/server/src/generation/promptBuilder.ut.test.ts（単体テストで追加）, apps/server/src/generation/tokenEstimator.ut.test.ts（単体テストで追加）</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6249,7 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 1：候補は buildPrompt の前に、外す前の参照する投稿で抽選する（設計書 1章・4章の順序どおり）。上限のために参照する投稿をすべて外すと、候補に reply・like が残ったまま、タイムラインが「（まだ投稿はありません）」になる（TC-UT_PRM-031）。LLM が reply・like を選ぶと P 番号が無く、検証で不正な形式になり再生成に回る。候補から外すか、このままでよいかを確認したい。</t>
+          <t>・疑い 1：候補は buildPrompt の前に、外す前の参照する投稿で抽選する。上限のために参照する投稿をすべて外すと、候補に reply・like が残ったまま、タイムラインが「（まだ投稿はありません）」になる（TC-UT_PRM-031）。2026-10-23、NOUS-102 で Kouhei Tajima が「外した後に参照できる投稿が無ければ reply・like を候補から外す」を仕様と決めたため、今の実装は仕様と食い違う。LLM が reply・like を選ぶと actionValidator で対象なしとして弾かれ、試行が無駄になる。そのときの動きは NOUS-103（actionValidator）の観点でも見る。</t>
         </is>
       </c>
     </row>
